--- a/tasks/finalpool/pw-sf-benchmark-excel-word-email/groundtruth_workspace/Benchmark_Analysis.xlsx
+++ b/tasks/finalpool/pw-sf-benchmark-excel-word-email/groundtruth_workspace/Benchmark_Analysis.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AVG of TOTAL_AMOUNT from SALES_DW.PUBLIC.ORDERS</t>
+          <t>AVG of order total amount in orders table</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AVG of SALARY from HR_ANALYTICS.PUBLIC.EMPLOYEES</t>
+          <t>AVG of salary in employees table</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AVG of JOB_SATISFACTION from HR_ANALYTICS.PUBLIC.EMPLOYEES</t>
+          <t>AVG of job satisfaction in employees table</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SUM(TOTAL_AMOUNT) / COUNT(EMPLOYEES)</t>
+          <t>SUM of order amounts / count of employees</t>
         </is>
       </c>
     </row>
